--- a/public/assets/ExpensesReport.xlsx
+++ b/public/assets/ExpensesReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ba157105b5202b/Desktop/Seva/JanmasthamiReport/public/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6EAC0E1-3160-496F-A0BF-183A7100A88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{A6EAC0E1-3160-496F-A0BF-183A7100A88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96A50940-0271-4A48-BF5C-1AB6D52AC8FB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="156">
   <si>
     <t>Phone</t>
   </si>
@@ -320,9 +320,6 @@
   </si>
   <si>
     <t>Auto charge for bringing bhoga</t>
-  </si>
-  <si>
-    <t>Banners and Donna</t>
   </si>
   <si>
     <t>Grocery for 4 bhoga</t>
@@ -493,6 +490,12 @@
   </si>
   <si>
     <t>Devotee</t>
+  </si>
+  <si>
+    <t>Banners</t>
+  </si>
+  <si>
+    <t>Donna</t>
   </si>
 </sst>
 </file>
@@ -886,9 +889,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -953,7 +956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1018,7 +1021,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1083,7 +1086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1148,7 +1151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -1213,7 +1216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1278,7 +1281,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -1343,7 +1346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1408,7 +1411,7 @@
         <v>12490</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1473,7 +1476,7 @@
         <v>8973</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -1538,7 +1541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -1603,7 +1606,7 @@
         <v>13424</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>56</v>
       </c>
@@ -1668,7 +1671,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -1733,7 +1736,7 @@
         <v>3770</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -1798,7 +1801,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>65</v>
       </c>
@@ -1863,7 +1866,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -1928,7 +1931,7 @@
         <v>14369</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>71</v>
       </c>
@@ -2004,7 +2007,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -2016,9 +2019,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>74</v>
       </c>
@@ -2056,7 +2059,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -2094,7 +2097,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -2142,7 +2145,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.5" bestFit="1" customWidth="1"/>
@@ -2153,7 +2156,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>80</v>
@@ -2170,24 +2173,22 @@
         <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="C2" s="1">
-        <v>920</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>95</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="C3" s="1">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>95</v>
@@ -2195,13 +2196,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C4" s="1">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>95</v>
@@ -2209,13 +2210,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C5" s="1">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>95</v>
@@ -2223,86 +2224,86 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C6" s="1">
-        <v>31000</v>
+        <v>1900</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C7" s="1">
-        <v>13000</v>
+        <v>31000</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C8" s="1">
-        <v>420</v>
+        <v>13000</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C9" s="1">
-        <v>544</v>
+        <v>420</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C10" s="1">
-        <v>1430</v>
+        <v>544</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C11" s="1">
-        <v>50</v>
+        <v>1430</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -2310,10 +2311,10 @@
         <v>48</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C12" s="1">
-        <v>240</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>95</v>
@@ -2324,10 +2325,10 @@
         <v>48</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C13" s="1">
-        <v>453</v>
+        <v>240</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>95</v>
@@ -2338,10 +2339,10 @@
         <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C14" s="1">
-        <v>190</v>
+        <v>453</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>95</v>
@@ -2352,10 +2353,10 @@
         <v>48</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C15" s="1">
-        <v>690</v>
+        <v>190</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>95</v>
@@ -2363,44 +2364,44 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C16" s="1">
-        <v>9000</v>
+        <v>690</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C17" s="1">
-        <v>300</v>
+        <v>9000</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C18" s="1">
-        <v>4625</v>
+        <v>300</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -2408,38 +2409,38 @@
         <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C19" s="1">
-        <v>200</v>
+        <v>4625</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C20" s="1">
-        <v>7500</v>
+        <v>200</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C21" s="1">
-        <v>2400</v>
+        <v>7500</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>95</v>
@@ -2447,13 +2448,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C22" s="1">
-        <v>2775</v>
+        <v>2400</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>95</v>
@@ -2461,13 +2462,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C23" s="1">
-        <v>2800</v>
+        <v>2775</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>95</v>
@@ -2475,13 +2476,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C24" s="1">
-        <v>160</v>
+        <v>2800</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>95</v>
@@ -2492,13 +2493,13 @@
         <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C25" s="1">
-        <v>1190</v>
+        <v>160</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>134</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -2506,80 +2507,80 @@
         <v>60</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C26" s="1">
-        <v>300</v>
+        <v>1190</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C27" s="1">
-        <v>2120</v>
+        <v>300</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C28" s="1">
-        <v>7350</v>
+        <v>2120</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C29" s="1">
-        <v>849</v>
+        <v>7350</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C30" s="1">
-        <v>424</v>
+        <v>849</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>45</v>
+        <v>143</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C31" s="1">
-        <v>1270</v>
+        <v>424</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>95</v>
@@ -2590,10 +2591,10 @@
         <v>45</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C32" s="1">
-        <v>5800</v>
+        <v>1270</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>95</v>
@@ -2604,13 +2605,13 @@
         <v>45</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C33" s="1">
-        <v>1200</v>
+        <v>5800</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -2618,13 +2619,13 @@
         <v>45</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C34" s="1">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -2632,13 +2633,13 @@
         <v>45</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C35" s="1">
-        <v>2500</v>
+        <v>600</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>95</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -2646,19 +2647,33 @@
         <v>45</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C36" s="1">
+        <v>2500</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C37" s="1">
         <v>200</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>95</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:C36 B1:C1 D2:D36" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:C37 B1:C1 D3:D37 A3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/assets/ExpensesReport.xlsx
+++ b/public/assets/ExpensesReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ba157105b5202b/Desktop/Seva/JanmasthamiReport/public/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{A6EAC0E1-3160-496F-A0BF-183A7100A88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96A50940-0271-4A48-BF5C-1AB6D52AC8FB}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{A6EAC0E1-3160-496F-A0BF-183A7100A88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{137D04BC-526F-454F-9B17-EAC88C2788F8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2608,7 +2608,7 @@
         <v>146</v>
       </c>
       <c r="C33" s="1">
-        <v>5800</v>
+        <v>3000</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>95</v>
@@ -2673,7 +2673,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A4:C37 B1:C1 D3:D37 A3" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:C32 B1:C1 D3:D37 A3 A34:C37 A33:B33" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>